--- a/LubanConfig/Moba/Production/Datas/J-角色表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-角色表.xlsx
@@ -63,12 +63,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -764,6 +767,64 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>孙尚香</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10070000</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10070101,10070201,10070301</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10080000</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10080101,10080201,10080301</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -775,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1716,6 +1777,166 @@
       <c r="AA9" s="2" t="n"/>
       <c r="AB9" s="2" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>10070001</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2" t="n"/>
+      <c r="AB10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10080001</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2" t="n"/>
+      <c r="AB11" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1727,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1790,6 +2011,26 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ValueMin</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ValueMax</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>DefaultValue</t>
         </is>
       </c>
@@ -1822,6 +2063,26 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
+          <t>ModifierFieldUnit</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),ModifierOp</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
@@ -1832,27 +2093,47 @@
           <t>##</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>本表记录的唯一 ID；其他表按该值引用。</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>稳定的程序标识或业务键；修改前检查代码与引用。</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>属性 ID；1-23 与 BattleAttributeType 枚举一一对应，发布后不可改动。</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>稳定的程序标识，必须等于 BattleAttributeType 枚举名；修改前检查代码与引用。</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>编辑器和调试时显示的名称。</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>属性值类型：Flat 为普通数值，Percent 为比率。</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>聚合方式：Flat 普通数值直接相加，Percent 比率按百分比参与计算。</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>量纲：Point 点数 / Distance 距离 / Ms 毫秒 / Count 次数 / Ratio 倍率 / Degrees 角度 / Percent 比率。</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>合法下界（含）。填 0 表示无下界。</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>合法上界（含）。填 0 表示无上界。</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>允许的修饰操作，逗号分隔：Add / Mul / Override / PercentAdd。</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>属性未被模板覆盖时使用的默认数值。</t>
         </is>
@@ -1873,12 +2154,23 @@
           <t>当前生命</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1897,12 +2189,23 @@
           <t>最大生命</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1921,12 +2224,23 @@
           <t>额外生命</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1945,12 +2259,23 @@
           <t>物理攻击</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1969,12 +2294,23 @@
           <t>法术攻击</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1993,12 +2329,23 @@
           <t>额外物理攻击</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2017,12 +2364,23 @@
           <t>额外法术攻击</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2041,12 +2399,23 @@
           <t>物理防御</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2065,12 +2434,23 @@
           <t>法术防御</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2089,12 +2469,23 @@
           <t>当前法力</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2113,12 +2504,23 @@
           <t>最大法力</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2137,12 +2539,23 @@
           <t>暴击率</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2161,12 +2574,23 @@
           <t>攻击速度加成</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2185,12 +2609,23 @@
           <t>冷却缩减</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2209,12 +2644,23 @@
           <t>物理穿透率</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2233,12 +2679,23 @@
           <t>法术穿透率</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2257,12 +2714,23 @@
           <t>移动速度</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2281,12 +2749,23 @@
           <t>物理吸血率</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2305,12 +2784,23 @@
           <t>法术吸血率</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2329,12 +2819,23 @@
           <t>攻击范围</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Add,Mul,Override</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2353,12 +2854,23 @@
           <t>每秒生命回复率</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2377,12 +2889,23 @@
           <t>每秒法力回复率</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2401,12 +2924,23 @@
           <t>韧性</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Add,Override</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
         <v>0</v>
       </c>
     </row>

--- a/LubanConfig/Moba/Production/Datas/J-角色表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-角色表.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -825,6 +825,48 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Melee Minion</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Ranged Minion</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -836,7 +878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1936,6 +1978,166 @@
       </c>
       <c r="AA11" s="2" t="n"/>
       <c r="AB11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>10010001</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2" t="n"/>
+      <c r="AB12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>10010001</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2" t="n"/>
+      <c r="AB13" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LubanConfig/Moba/Production/Datas/J-角色表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-角色表.xlsx
@@ -878,7 +878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1046,12 +1046,117 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>OmittedFields</t>
+          <t>HpGrowth</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>NullFields</t>
+          <t>MaxHpGrowth</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ExtraHpGrowth</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>PhysicsAttackGrowth</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>MagicAttackGrowth</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ExtraPhysicsAttackGrowth</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ExtraMagicAttackGrowth</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>PhysicsDefenseGrowth</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>MagicDefenseGrowth</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ManaGrowth</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>MaxManaGrowth</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>CriticalRGrowth</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>AttackSpeedRGrowth</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>CooldownReduceRGrowth</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>PhysicsPenetrationRGrowth</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>MagicPenetrationRGrowth</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>MoveSpeedGrowth</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>PhysicsBloodsuckingRGrowth</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>MagicBloodsuckingRGrowth</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>AttackRangeGrowth</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>PerSecondBloodRGrowth</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>PerSecondManaRGrowth</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>ResilienceRGrowth</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1293,117 @@
       </c>
       <c r="AA2" s="1" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1540,117 @@
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>迁移兼容字段：逗号分隔的原 JSON 缺失字段名；新数据通常留空。</t>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>迁移兼容字段：逗号分隔的原 JSON 显式 null 字段名；新数据通常留空。</t>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per-level growth; final value = base + growth * (level - 1). Zero disables growth for the attribute.</t>
         </is>
       </c>
     </row>
@@ -1416,8 +1731,75 @@
       <c r="Z4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" s="2" t="n"/>
-      <c r="AB4" s="2" t="n"/>
+      <c r="AA4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -1496,8 +1878,75 @@
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n"/>
-      <c r="AB5" s="2" t="n"/>
+      <c r="AA5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -1576,8 +2025,75 @@
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" s="2" t="n"/>
-      <c r="AB6" s="2" t="n"/>
+      <c r="AA6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1656,8 +2172,75 @@
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" s="2" t="n"/>
-      <c r="AB7" s="2" t="n"/>
+      <c r="AA7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1736,8 +2319,75 @@
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" s="2" t="n"/>
-      <c r="AB8" s="2" t="n"/>
+      <c r="AA8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1816,8 +2466,75 @@
       <c r="Z9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA9" s="2" t="n"/>
-      <c r="AB9" s="2" t="n"/>
+      <c r="AA9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1896,8 +2613,75 @@
       <c r="Z10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA10" s="2" t="n"/>
-      <c r="AB10" s="2" t="n"/>
+      <c r="AA10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1976,8 +2760,75 @@
       <c r="Z11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA11" s="2" t="n"/>
-      <c r="AB11" s="2" t="n"/>
+      <c r="AA11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -2056,8 +2907,75 @@
       <c r="Z12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA12" s="2" t="n"/>
-      <c r="AB12" s="2" t="n"/>
+      <c r="AA12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -2136,8 +3054,75 @@
       <c r="Z13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA13" s="2" t="n"/>
-      <c r="AB13" s="2" t="n"/>
+      <c r="AA13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
